--- a/event_planner_forms/013_event_venue_communication_form--event_planner_forms.xlsx
+++ b/event_planner_forms/013_event_venue_communication_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'jim',_'label':_'jim'}</t>
+          <t>jim</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Jim', 'label': 'Jim'}</t>
+          <t>Jim</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'jane',_'label':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Jane', 'label': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'conference',_'label':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Conference', 'label': 'Conference'}</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'meeting',_'label':_'meeting'}</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Meeting', 'label': 'Meeting'}</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'event',_'label':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Event', 'label': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'High', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'High', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
